--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR_VACT.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR_VACT.xlsx
@@ -4535,29 +4535,14 @@
     <xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4565,14 +4550,23 @@
     <xf numFmtId="0" fontId="1" fillId="46" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4581,6 +4575,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4601,40 +4610,7 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4658,8 +4634,51 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="53" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="84" fillId="62" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="63" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="64" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="60" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4673,7 +4692,6 @@
     <xf numFmtId="0" fontId="84" fillId="50" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="53" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="84" fillId="54" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4681,15 +4699,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="58" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="62" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="63" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="64" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4700,15 +4709,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -14021,11 +14021,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="265"/>
-      <c r="E3" s="394" t="s">
+      <c r="E3" s="397" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="395"/>
-      <c r="G3" s="396"/>
+      <c r="F3" s="398"/>
+      <c r="G3" s="399"/>
       <c r="H3" s="263" t="s">
         <v>8</v>
       </c>
@@ -17069,21 +17069,21 @@
       <c r="C20" s="118" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="397" t="s">
+      <c r="D20" s="400" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="397"/>
-      <c r="F20" s="397"/>
-      <c r="G20" s="398" t="s">
+      <c r="E20" s="400"/>
+      <c r="F20" s="400"/>
+      <c r="G20" s="401" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="398"/>
-      <c r="I20" s="398"/>
-      <c r="J20" s="399" t="s">
+      <c r="H20" s="401"/>
+      <c r="I20" s="401"/>
+      <c r="J20" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="399"/>
-      <c r="L20" s="399"/>
+      <c r="K20" s="402"/>
+      <c r="L20" s="402"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="143"/>
@@ -20527,43 +20527,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="381" t="s">
+      <c r="O3" s="394" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="381"/>
-      <c r="Q3" s="381"/>
-      <c r="R3" s="381"/>
-      <c r="S3" s="381"/>
-      <c r="T3" s="381"/>
-      <c r="U3" s="381"/>
-      <c r="V3" s="381"/>
-      <c r="W3" s="381"/>
-      <c r="X3" s="381"/>
-      <c r="Y3" s="381"/>
-      <c r="Z3" s="381"/>
-      <c r="AA3" s="381"/>
-      <c r="AB3" s="381"/>
-      <c r="AC3" s="381"/>
+      <c r="P3" s="394"/>
+      <c r="Q3" s="394"/>
+      <c r="R3" s="394"/>
+      <c r="S3" s="394"/>
+      <c r="T3" s="394"/>
+      <c r="U3" s="394"/>
+      <c r="V3" s="394"/>
+      <c r="W3" s="394"/>
+      <c r="X3" s="394"/>
+      <c r="Y3" s="394"/>
+      <c r="Z3" s="394"/>
+      <c r="AA3" s="394"/>
+      <c r="AB3" s="394"/>
+      <c r="AC3" s="394"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="381"/>
-      <c r="P4" s="381"/>
-      <c r="Q4" s="381"/>
-      <c r="R4" s="381"/>
-      <c r="S4" s="381"/>
-      <c r="T4" s="381"/>
-      <c r="U4" s="381"/>
-      <c r="V4" s="381"/>
-      <c r="W4" s="381"/>
-      <c r="X4" s="381"/>
-      <c r="Y4" s="381"/>
-      <c r="Z4" s="381"/>
-      <c r="AA4" s="381"/>
-      <c r="AB4" s="381"/>
-      <c r="AC4" s="381"/>
+      <c r="O4" s="394"/>
+      <c r="P4" s="394"/>
+      <c r="Q4" s="394"/>
+      <c r="R4" s="394"/>
+      <c r="S4" s="394"/>
+      <c r="T4" s="394"/>
+      <c r="U4" s="394"/>
+      <c r="V4" s="394"/>
+      <c r="W4" s="394"/>
+      <c r="X4" s="394"/>
+      <c r="Y4" s="394"/>
+      <c r="Z4" s="394"/>
+      <c r="AA4" s="394"/>
+      <c r="AB4" s="394"/>
+      <c r="AC4" s="394"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -20592,17 +20592,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="75"/>
-      <c r="J8" s="408" t="s">
+      <c r="J8" s="403" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="408"/>
-      <c r="L8" s="408"/>
-      <c r="M8" s="408"/>
-      <c r="N8" s="408"/>
-      <c r="O8" s="408"/>
-      <c r="P8" s="408"/>
-      <c r="Q8" s="408"/>
-      <c r="R8" s="408"/>
+      <c r="K8" s="403"/>
+      <c r="L8" s="403"/>
+      <c r="M8" s="403"/>
+      <c r="N8" s="403"/>
+      <c r="O8" s="403"/>
+      <c r="P8" s="403"/>
+      <c r="Q8" s="403"/>
+      <c r="R8" s="403"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -20617,168 +20617,168 @@
       <c r="Z8" s="73"/>
       <c r="AA8" s="73"/>
       <c r="AB8" s="73"/>
-      <c r="AC8" s="412" t="s">
+      <c r="AC8" s="404" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="413"/>
-      <c r="AE8" s="413"/>
-      <c r="AF8" s="413"/>
-      <c r="AG8" s="413"/>
-      <c r="AH8" s="414"/>
-      <c r="AI8" s="415" t="s">
+      <c r="AD8" s="405"/>
+      <c r="AE8" s="405"/>
+      <c r="AF8" s="405"/>
+      <c r="AG8" s="405"/>
+      <c r="AH8" s="406"/>
+      <c r="AI8" s="407" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="167"/>
       <c r="AK8" s="167"/>
-      <c r="AL8" s="417" t="s">
+      <c r="AL8" s="409" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="418"/>
-      <c r="AN8" s="418"/>
-      <c r="AO8" s="418"/>
-      <c r="AP8" s="418"/>
-      <c r="AQ8" s="418"/>
-      <c r="AR8" s="405" t="s">
+      <c r="AM8" s="410"/>
+      <c r="AN8" s="410"/>
+      <c r="AO8" s="410"/>
+      <c r="AP8" s="410"/>
+      <c r="AQ8" s="410"/>
+      <c r="AR8" s="414" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="405"/>
-      <c r="AT8" s="405"/>
-      <c r="AU8" s="405"/>
-      <c r="AV8" s="405"/>
-      <c r="AW8" s="405"/>
-      <c r="AX8" s="405"/>
-      <c r="AY8" s="405"/>
-      <c r="AZ8" s="405"/>
+      <c r="AS8" s="414"/>
+      <c r="AT8" s="414"/>
+      <c r="AU8" s="414"/>
+      <c r="AV8" s="414"/>
+      <c r="AW8" s="414"/>
+      <c r="AX8" s="414"/>
+      <c r="AY8" s="414"/>
+      <c r="AZ8" s="414"/>
       <c r="BA8" s="171"/>
       <c r="BB8" s="171"/>
       <c r="BC8" s="171"/>
-      <c r="BD8" s="402" t="s">
+      <c r="BD8" s="420" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="402"/>
-      <c r="BF8" s="402"/>
-      <c r="BG8" s="402"/>
-      <c r="BH8" s="402"/>
-      <c r="BI8" s="402"/>
-      <c r="BJ8" s="402"/>
-      <c r="BK8" s="402"/>
-      <c r="BL8" s="402"/>
-      <c r="BM8" s="402"/>
-      <c r="BN8" s="402"/>
-      <c r="BO8" s="402"/>
-      <c r="BP8" s="402"/>
-      <c r="BQ8" s="392" t="s">
+      <c r="BE8" s="420"/>
+      <c r="BF8" s="420"/>
+      <c r="BG8" s="420"/>
+      <c r="BH8" s="420"/>
+      <c r="BI8" s="420"/>
+      <c r="BJ8" s="420"/>
+      <c r="BK8" s="420"/>
+      <c r="BL8" s="420"/>
+      <c r="BM8" s="420"/>
+      <c r="BN8" s="420"/>
+      <c r="BO8" s="420"/>
+      <c r="BP8" s="420"/>
+      <c r="BQ8" s="390" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="392"/>
-      <c r="BS8" s="392"/>
+      <c r="BR8" s="390"/>
+      <c r="BS8" s="390"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="407" t="s">
+      <c r="C9" s="416" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="407"/>
-      <c r="E9" s="407"/>
-      <c r="F9" s="407"/>
-      <c r="G9" s="407"/>
-      <c r="H9" s="407"/>
-      <c r="I9" s="407"/>
-      <c r="J9" s="408" t="s">
+      <c r="D9" s="416"/>
+      <c r="E9" s="416"/>
+      <c r="F9" s="416"/>
+      <c r="G9" s="416"/>
+      <c r="H9" s="416"/>
+      <c r="I9" s="416"/>
+      <c r="J9" s="403" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="408"/>
-      <c r="L9" s="408"/>
-      <c r="M9" s="408"/>
-      <c r="N9" s="408"/>
-      <c r="O9" s="408"/>
-      <c r="P9" s="408"/>
-      <c r="Q9" s="408"/>
-      <c r="R9" s="408"/>
-      <c r="S9" s="409" t="s">
+      <c r="K9" s="403"/>
+      <c r="L9" s="403"/>
+      <c r="M9" s="403"/>
+      <c r="N9" s="403"/>
+      <c r="O9" s="403"/>
+      <c r="P9" s="403"/>
+      <c r="Q9" s="403"/>
+      <c r="R9" s="403"/>
+      <c r="S9" s="417" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="410" t="s">
+      <c r="T9" s="411" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="410" t="s">
+      <c r="U9" s="411" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="410" t="s">
+      <c r="V9" s="411" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="180"/>
       <c r="X9" s="180"/>
       <c r="Y9" s="180"/>
       <c r="Z9" s="180"/>
-      <c r="AA9" s="412" t="s">
+      <c r="AA9" s="404" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="413"/>
-      <c r="AC9" s="413"/>
-      <c r="AD9" s="413"/>
-      <c r="AE9" s="413"/>
-      <c r="AF9" s="413"/>
-      <c r="AG9" s="413"/>
-      <c r="AH9" s="414"/>
-      <c r="AI9" s="416"/>
+      <c r="AB9" s="405"/>
+      <c r="AC9" s="405"/>
+      <c r="AD9" s="405"/>
+      <c r="AE9" s="405"/>
+      <c r="AF9" s="405"/>
+      <c r="AG9" s="405"/>
+      <c r="AH9" s="406"/>
+      <c r="AI9" s="408"/>
       <c r="AJ9" s="169"/>
       <c r="AK9" s="169"/>
-      <c r="AL9" s="419" t="s">
+      <c r="AL9" s="413" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="419"/>
-      <c r="AN9" s="419"/>
-      <c r="AO9" s="419"/>
-      <c r="AP9" s="419"/>
-      <c r="AQ9" s="419"/>
-      <c r="AR9" s="406" t="s">
+      <c r="AM9" s="413"/>
+      <c r="AN9" s="413"/>
+      <c r="AO9" s="413"/>
+      <c r="AP9" s="413"/>
+      <c r="AQ9" s="413"/>
+      <c r="AR9" s="415" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="406"/>
-      <c r="AT9" s="406"/>
-      <c r="AU9" s="406"/>
-      <c r="AV9" s="406"/>
-      <c r="AW9" s="406"/>
-      <c r="AX9" s="406"/>
-      <c r="AY9" s="406"/>
-      <c r="AZ9" s="406"/>
+      <c r="AS9" s="415"/>
+      <c r="AT9" s="415"/>
+      <c r="AU9" s="415"/>
+      <c r="AV9" s="415"/>
+      <c r="AW9" s="415"/>
+      <c r="AX9" s="415"/>
+      <c r="AY9" s="415"/>
+      <c r="AZ9" s="415"/>
       <c r="BA9" s="172"/>
       <c r="BB9" s="172"/>
       <c r="BC9" s="172"/>
-      <c r="BD9" s="403" t="s">
+      <c r="BD9" s="421" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="403"/>
-      <c r="BF9" s="403"/>
-      <c r="BG9" s="403"/>
-      <c r="BH9" s="403"/>
-      <c r="BI9" s="403"/>
-      <c r="BJ9" s="403"/>
-      <c r="BK9" s="403"/>
-      <c r="BL9" s="403"/>
-      <c r="BM9" s="403"/>
-      <c r="BN9" s="403"/>
-      <c r="BO9" s="403"/>
-      <c r="BP9" s="403"/>
-      <c r="BQ9" s="404" t="s">
+      <c r="BE9" s="421"/>
+      <c r="BF9" s="421"/>
+      <c r="BG9" s="421"/>
+      <c r="BH9" s="421"/>
+      <c r="BI9" s="421"/>
+      <c r="BJ9" s="421"/>
+      <c r="BK9" s="421"/>
+      <c r="BL9" s="421"/>
+      <c r="BM9" s="421"/>
+      <c r="BN9" s="421"/>
+      <c r="BO9" s="421"/>
+      <c r="BP9" s="421"/>
+      <c r="BQ9" s="422" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="404"/>
-      <c r="BS9" s="404"/>
-      <c r="BT9" s="400" t="s">
+      <c r="BR9" s="422"/>
+      <c r="BS9" s="422"/>
+      <c r="BT9" s="418" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="400" t="s">
+      <c r="BU9" s="418" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="400" t="s">
+      <c r="BV9" s="418" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="401" t="s">
+      <c r="BW9" s="419" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -20834,10 +20834,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="409"/>
-      <c r="T10" s="411"/>
-      <c r="U10" s="411"/>
-      <c r="V10" s="411"/>
+      <c r="S10" s="417"/>
+      <c r="T10" s="412"/>
+      <c r="U10" s="412"/>
+      <c r="V10" s="412"/>
       <c r="W10" s="170" t="s">
         <v>205</v>
       </c>
@@ -20963,10 +20963,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="400"/>
-      <c r="BU10" s="400"/>
-      <c r="BV10" s="400"/>
-      <c r="BW10" s="401"/>
+      <c r="BT10" s="418"/>
+      <c r="BU10" s="418"/>
+      <c r="BV10" s="418"/>
+      <c r="BW10" s="419"/>
     </row>
     <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -37991,6 +37991,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -37999,21 +38014,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="618" priority="1" operator="containsText" text="En Proceso">
@@ -38107,9 +38107,9 @@
       <c r="W3" s="309" t="s">
         <v>396</v>
       </c>
-      <c r="AI3" s="381"/>
-      <c r="AJ3" s="381"/>
-      <c r="AK3" s="381"/>
+      <c r="AI3" s="394"/>
+      <c r="AJ3" s="394"/>
+      <c r="AK3" s="394"/>
       <c r="AL3" s="75"/>
       <c r="AM3" s="75"/>
       <c r="AN3" s="75"/>
@@ -38126,9 +38126,9 @@
       <c r="W4" s="309" t="s">
         <v>396</v>
       </c>
-      <c r="AI4" s="381"/>
-      <c r="AJ4" s="381"/>
-      <c r="AK4" s="381"/>
+      <c r="AI4" s="394"/>
+      <c r="AJ4" s="394"/>
+      <c r="AK4" s="394"/>
       <c r="AL4" s="75"/>
       <c r="AM4" s="75"/>
       <c r="AN4" s="75"/>
@@ -38169,118 +38169,118 @@
       </c>
     </row>
     <row r="8" spans="3:49" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="391" t="s">
+      <c r="C8" s="389" t="s">
         <v>540</v>
       </c>
-      <c r="D8" s="392"/>
-      <c r="E8" s="392"/>
-      <c r="F8" s="392"/>
-      <c r="G8" s="392"/>
-      <c r="H8" s="392"/>
-      <c r="I8" s="392"/>
-      <c r="J8" s="392"/>
-      <c r="K8" s="393"/>
-      <c r="L8" s="434" t="s">
+      <c r="D8" s="390"/>
+      <c r="E8" s="390"/>
+      <c r="F8" s="390"/>
+      <c r="G8" s="390"/>
+      <c r="H8" s="390"/>
+      <c r="I8" s="390"/>
+      <c r="J8" s="390"/>
+      <c r="K8" s="391"/>
+      <c r="L8" s="378" t="s">
         <v>415</v>
       </c>
-      <c r="M8" s="435"/>
-      <c r="N8" s="435"/>
-      <c r="O8" s="435"/>
-      <c r="P8" s="435"/>
-      <c r="Q8" s="436"/>
-      <c r="R8" s="386" t="s">
+      <c r="M8" s="379"/>
+      <c r="N8" s="379"/>
+      <c r="O8" s="379"/>
+      <c r="P8" s="379"/>
+      <c r="Q8" s="380"/>
+      <c r="R8" s="381" t="s">
         <v>363</v>
       </c>
-      <c r="S8" s="387"/>
-      <c r="T8" s="387"/>
-      <c r="U8" s="387"/>
-      <c r="V8" s="387"/>
-      <c r="W8" s="387"/>
-      <c r="X8" s="387"/>
-      <c r="Y8" s="387"/>
-      <c r="Z8" s="387"/>
-      <c r="AA8" s="387"/>
-      <c r="AB8" s="387"/>
-      <c r="AC8" s="389"/>
-      <c r="AD8" s="386" t="s">
+      <c r="S8" s="382"/>
+      <c r="T8" s="382"/>
+      <c r="U8" s="382"/>
+      <c r="V8" s="382"/>
+      <c r="W8" s="382"/>
+      <c r="X8" s="382"/>
+      <c r="Y8" s="382"/>
+      <c r="Z8" s="382"/>
+      <c r="AA8" s="382"/>
+      <c r="AB8" s="382"/>
+      <c r="AC8" s="392"/>
+      <c r="AD8" s="381" t="s">
         <v>417</v>
       </c>
-      <c r="AE8" s="387"/>
-      <c r="AF8" s="387"/>
-      <c r="AG8" s="387"/>
-      <c r="AH8" s="387"/>
-      <c r="AI8" s="387"/>
-      <c r="AJ8" s="387"/>
-      <c r="AK8" s="387"/>
-      <c r="AL8" s="387"/>
-      <c r="AM8" s="387"/>
-      <c r="AN8" s="387"/>
-      <c r="AO8" s="387"/>
-      <c r="AP8" s="387"/>
-      <c r="AQ8" s="387"/>
-      <c r="AR8" s="387"/>
-      <c r="AS8" s="389"/>
-      <c r="AT8" s="386" t="s">
+      <c r="AE8" s="382"/>
+      <c r="AF8" s="382"/>
+      <c r="AG8" s="382"/>
+      <c r="AH8" s="382"/>
+      <c r="AI8" s="382"/>
+      <c r="AJ8" s="382"/>
+      <c r="AK8" s="382"/>
+      <c r="AL8" s="382"/>
+      <c r="AM8" s="382"/>
+      <c r="AN8" s="382"/>
+      <c r="AO8" s="382"/>
+      <c r="AP8" s="382"/>
+      <c r="AQ8" s="382"/>
+      <c r="AR8" s="382"/>
+      <c r="AS8" s="392"/>
+      <c r="AT8" s="381" t="s">
         <v>419</v>
       </c>
-      <c r="AU8" s="387"/>
+      <c r="AU8" s="382"/>
       <c r="AV8" s="328"/>
       <c r="AW8" s="328"/>
     </row>
     <row r="9" spans="3:49" s="300" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="378" t="s">
+      <c r="C9" s="387" t="s">
         <v>410</v>
       </c>
-      <c r="D9" s="379"/>
-      <c r="E9" s="379"/>
-      <c r="F9" s="379"/>
-      <c r="G9" s="379"/>
-      <c r="H9" s="379"/>
-      <c r="I9" s="379"/>
-      <c r="J9" s="379"/>
-      <c r="K9" s="379"/>
-      <c r="L9" s="383" t="s">
+      <c r="D9" s="388"/>
+      <c r="E9" s="388"/>
+      <c r="F9" s="388"/>
+      <c r="G9" s="388"/>
+      <c r="H9" s="388"/>
+      <c r="I9" s="388"/>
+      <c r="J9" s="388"/>
+      <c r="K9" s="388"/>
+      <c r="L9" s="395" t="s">
         <v>416</v>
       </c>
-      <c r="M9" s="383"/>
-      <c r="N9" s="383"/>
-      <c r="O9" s="383"/>
-      <c r="P9" s="384"/>
+      <c r="M9" s="395"/>
+      <c r="N9" s="395"/>
+      <c r="O9" s="395"/>
+      <c r="P9" s="396"/>
       <c r="Q9" s="314"/>
-      <c r="R9" s="382" t="s">
+      <c r="R9" s="383" t="s">
         <v>411</v>
       </c>
-      <c r="S9" s="385"/>
-      <c r="T9" s="383"/>
-      <c r="U9" s="383"/>
-      <c r="V9" s="384"/>
+      <c r="S9" s="384"/>
+      <c r="T9" s="395"/>
+      <c r="U9" s="395"/>
+      <c r="V9" s="396"/>
       <c r="W9" s="318" t="s">
         <v>402</v>
       </c>
       <c r="X9" s="318" t="s">
         <v>369</v>
       </c>
-      <c r="Y9" s="382" t="s">
+      <c r="Y9" s="383" t="s">
         <v>198</v>
       </c>
-      <c r="Z9" s="385"/>
-      <c r="AA9" s="385"/>
-      <c r="AB9" s="388"/>
+      <c r="Z9" s="384"/>
+      <c r="AA9" s="384"/>
+      <c r="AB9" s="385"/>
       <c r="AC9" s="314"/>
-      <c r="AD9" s="390" t="s">
+      <c r="AD9" s="386" t="s">
         <v>412</v>
       </c>
-      <c r="AE9" s="390"/>
-      <c r="AF9" s="390"/>
-      <c r="AG9" s="382" t="s">
+      <c r="AE9" s="386"/>
+      <c r="AF9" s="386"/>
+      <c r="AG9" s="383" t="s">
         <v>413</v>
       </c>
-      <c r="AH9" s="388"/>
-      <c r="AI9" s="382" t="s">
+      <c r="AH9" s="385"/>
+      <c r="AI9" s="383" t="s">
         <v>414</v>
       </c>
-      <c r="AJ9" s="385"/>
-      <c r="AK9" s="388"/>
+      <c r="AJ9" s="384"/>
+      <c r="AK9" s="385"/>
       <c r="AL9" s="327" t="s">
         <v>403</v>
       </c>
@@ -38291,25 +38291,25 @@
       <c r="AQ9" s="325"/>
       <c r="AR9" s="326"/>
       <c r="AS9" s="314"/>
-      <c r="AT9" s="382" t="s">
+      <c r="AT9" s="383" t="s">
         <v>418</v>
       </c>
-      <c r="AU9" s="388"/>
+      <c r="AU9" s="385"/>
       <c r="AV9" s="314"/>
       <c r="AW9" s="328"/>
     </row>
     <row r="10" spans="3:49" s="300" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="378" t="s">
+      <c r="C10" s="387" t="s">
         <v>555</v>
       </c>
-      <c r="D10" s="379"/>
-      <c r="E10" s="379"/>
-      <c r="F10" s="379"/>
-      <c r="G10" s="379"/>
-      <c r="H10" s="379"/>
-      <c r="I10" s="379"/>
-      <c r="J10" s="379"/>
-      <c r="K10" s="380"/>
+      <c r="D10" s="388"/>
+      <c r="E10" s="388"/>
+      <c r="F10" s="388"/>
+      <c r="G10" s="388"/>
+      <c r="H10" s="388"/>
+      <c r="I10" s="388"/>
+      <c r="J10" s="388"/>
+      <c r="K10" s="393"/>
       <c r="L10" s="317" t="s">
         <v>380</v>
       </c>
@@ -47469,6 +47469,12 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="14">
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="AI3:AK4"/>
+    <mergeCell ref="L9:P9"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AG9:AH9"/>
     <mergeCell ref="AT8:AU8"/>
     <mergeCell ref="Y9:AB9"/>
     <mergeCell ref="AD9:AF9"/>
@@ -47477,19 +47483,13 @@
     <mergeCell ref="C8:K8"/>
     <mergeCell ref="R8:AC8"/>
     <mergeCell ref="AD8:AS8"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="AI3:AK4"/>
-    <mergeCell ref="L9:P9"/>
-    <mergeCell ref="R9:V9"/>
-    <mergeCell ref="AI9:AK9"/>
-    <mergeCell ref="AG9:AH9"/>
   </mergeCells>
-  <conditionalFormatting sqref="L8 R9:S9 M10 V10 AM47:AP48 V57 AG57:AG58 V59:V61 AG60 AG66 V68 R8">
+  <conditionalFormatting sqref="L8 R8 R9:S9 M10 V10 AM47:AP48 V57 AG57:AG58 V59:V61 AG60 AG66 V68">
     <cfRule type="cellIs" dxfId="615" priority="3281" operator="equal">
       <formula>"en proceso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L8 R9:S9 M10 V10 AM47:AP48 AG57:AG58 AG60 AG66 R8">
+  <conditionalFormatting sqref="L8 R8 R9:S9 M10 V10 AM47:AP48 AG57:AG58 AG60 AG66">
     <cfRule type="cellIs" dxfId="614" priority="3283" operator="equal">
       <formula>"finalizado"</formula>
     </cfRule>
@@ -50189,30 +50189,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="421" t="s">
+      <c r="A1" s="428" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="421"/>
-      <c r="C1" s="421"/>
-      <c r="D1" s="421"/>
-      <c r="E1" s="421"/>
-      <c r="F1" s="421"/>
-      <c r="G1" s="421"/>
-      <c r="H1" s="421"/>
-      <c r="I1" s="421"/>
+      <c r="B1" s="428"/>
+      <c r="C1" s="428"/>
+      <c r="D1" s="428"/>
+      <c r="E1" s="428"/>
+      <c r="F1" s="428"/>
+      <c r="G1" s="428"/>
+      <c r="H1" s="428"/>
+      <c r="I1" s="428"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="422" t="s">
+      <c r="A2" s="429" t="s">
         <v>429</v>
       </c>
-      <c r="B2" s="422"/>
-      <c r="C2" s="422"/>
-      <c r="D2" s="422"/>
-      <c r="E2" s="422"/>
-      <c r="F2" s="422"/>
-      <c r="G2" s="422"/>
-      <c r="H2" s="422"/>
-      <c r="I2" s="422"/>
+      <c r="B2" s="429"/>
+      <c r="C2" s="429"/>
+      <c r="D2" s="429"/>
+      <c r="E2" s="429"/>
+      <c r="F2" s="429"/>
+      <c r="G2" s="429"/>
+      <c r="H2" s="429"/>
+      <c r="I2" s="429"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="330" t="s">
@@ -50268,17 +50268,17 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="423" t="s">
+      <c r="A7" s="430" t="s">
         <v>438</v>
       </c>
-      <c r="B7" s="423"/>
-      <c r="C7" s="423"/>
-      <c r="D7" s="423"/>
-      <c r="E7" s="423"/>
-      <c r="F7" s="423"/>
-      <c r="G7" s="423"/>
-      <c r="H7" s="423"/>
-      <c r="I7" s="423"/>
+      <c r="B7" s="430"/>
+      <c r="C7" s="430"/>
+      <c r="D7" s="430"/>
+      <c r="E7" s="430"/>
+      <c r="F7" s="430"/>
+      <c r="G7" s="430"/>
+      <c r="H7" s="430"/>
+      <c r="I7" s="430"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="332">
@@ -50414,28 +50414,28 @@
       <c r="I14" s="337"/>
     </row>
     <row r="15" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="424"/>
-      <c r="B15" s="424"/>
-      <c r="C15" s="424"/>
-      <c r="D15" s="424"/>
-      <c r="E15" s="424"/>
-      <c r="F15" s="424"/>
-      <c r="G15" s="424"/>
-      <c r="H15" s="424"/>
-      <c r="I15" s="424"/>
+      <c r="A15" s="423"/>
+      <c r="B15" s="423"/>
+      <c r="C15" s="423"/>
+      <c r="D15" s="423"/>
+      <c r="E15" s="423"/>
+      <c r="F15" s="423"/>
+      <c r="G15" s="423"/>
+      <c r="H15" s="423"/>
+      <c r="I15" s="423"/>
     </row>
     <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="425" t="s">
+      <c r="A16" s="431" t="s">
         <v>453</v>
       </c>
-      <c r="B16" s="425"/>
-      <c r="C16" s="425"/>
-      <c r="D16" s="425"/>
-      <c r="E16" s="425"/>
-      <c r="F16" s="425"/>
-      <c r="G16" s="425"/>
-      <c r="H16" s="425"/>
-      <c r="I16" s="425"/>
+      <c r="B16" s="431"/>
+      <c r="C16" s="431"/>
+      <c r="D16" s="431"/>
+      <c r="E16" s="431"/>
+      <c r="F16" s="431"/>
+      <c r="G16" s="431"/>
+      <c r="H16" s="431"/>
+      <c r="I16" s="431"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="344">
@@ -50514,28 +50514,28 @@
       <c r="I20" s="343"/>
     </row>
     <row r="21" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="424"/>
-      <c r="B21" s="424"/>
-      <c r="C21" s="424"/>
-      <c r="D21" s="424"/>
-      <c r="E21" s="424"/>
-      <c r="F21" s="424"/>
-      <c r="G21" s="424"/>
-      <c r="H21" s="424"/>
-      <c r="I21" s="424"/>
+      <c r="A21" s="423"/>
+      <c r="B21" s="423"/>
+      <c r="C21" s="423"/>
+      <c r="D21" s="423"/>
+      <c r="E21" s="423"/>
+      <c r="F21" s="423"/>
+      <c r="G21" s="423"/>
+      <c r="H21" s="423"/>
+      <c r="I21" s="423"/>
     </row>
     <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="426" t="s">
+      <c r="A22" s="432" t="s">
         <v>461</v>
       </c>
-      <c r="B22" s="426"/>
-      <c r="C22" s="426"/>
-      <c r="D22" s="426"/>
-      <c r="E22" s="426"/>
-      <c r="F22" s="426"/>
-      <c r="G22" s="426"/>
-      <c r="H22" s="426"/>
-      <c r="I22" s="426"/>
+      <c r="B22" s="432"/>
+      <c r="C22" s="432"/>
+      <c r="D22" s="432"/>
+      <c r="E22" s="432"/>
+      <c r="F22" s="432"/>
+      <c r="G22" s="432"/>
+      <c r="H22" s="432"/>
+      <c r="I22" s="432"/>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="350">
@@ -50709,28 +50709,28 @@
       <c r="I31" s="355"/>
     </row>
     <row r="32" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="424"/>
-      <c r="B32" s="424"/>
-      <c r="C32" s="424"/>
-      <c r="D32" s="424"/>
-      <c r="E32" s="424"/>
-      <c r="F32" s="424"/>
-      <c r="G32" s="424"/>
-      <c r="H32" s="424"/>
-      <c r="I32" s="424"/>
+      <c r="A32" s="423"/>
+      <c r="B32" s="423"/>
+      <c r="C32" s="423"/>
+      <c r="D32" s="423"/>
+      <c r="E32" s="423"/>
+      <c r="F32" s="423"/>
+      <c r="G32" s="423"/>
+      <c r="H32" s="423"/>
+      <c r="I32" s="423"/>
     </row>
     <row r="33" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="427" t="s">
+      <c r="A33" s="433" t="s">
         <v>478</v>
       </c>
-      <c r="B33" s="427"/>
-      <c r="C33" s="427"/>
-      <c r="D33" s="427"/>
-      <c r="E33" s="427"/>
-      <c r="F33" s="427"/>
-      <c r="G33" s="427"/>
-      <c r="H33" s="427"/>
-      <c r="I33" s="427"/>
+      <c r="B33" s="433"/>
+      <c r="C33" s="433"/>
+      <c r="D33" s="433"/>
+      <c r="E33" s="433"/>
+      <c r="F33" s="433"/>
+      <c r="G33" s="433"/>
+      <c r="H33" s="433"/>
+      <c r="I33" s="433"/>
     </row>
     <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="356">
@@ -50790,28 +50790,28 @@
       <c r="I36" s="361"/>
     </row>
     <row r="37" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="424"/>
-      <c r="B37" s="424"/>
-      <c r="C37" s="424"/>
-      <c r="D37" s="424"/>
-      <c r="E37" s="424"/>
-      <c r="F37" s="424"/>
-      <c r="G37" s="424"/>
-      <c r="H37" s="424"/>
-      <c r="I37" s="424"/>
+      <c r="A37" s="423"/>
+      <c r="B37" s="423"/>
+      <c r="C37" s="423"/>
+      <c r="D37" s="423"/>
+      <c r="E37" s="423"/>
+      <c r="F37" s="423"/>
+      <c r="G37" s="423"/>
+      <c r="H37" s="423"/>
+      <c r="I37" s="423"/>
     </row>
     <row r="38" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="420" t="s">
+      <c r="A38" s="427" t="s">
         <v>484</v>
       </c>
-      <c r="B38" s="420"/>
-      <c r="C38" s="420"/>
-      <c r="D38" s="420"/>
-      <c r="E38" s="420"/>
-      <c r="F38" s="420"/>
-      <c r="G38" s="420"/>
-      <c r="H38" s="420"/>
-      <c r="I38" s="420"/>
+      <c r="B38" s="427"/>
+      <c r="C38" s="427"/>
+      <c r="D38" s="427"/>
+      <c r="E38" s="427"/>
+      <c r="F38" s="427"/>
+      <c r="G38" s="427"/>
+      <c r="H38" s="427"/>
+      <c r="I38" s="427"/>
     </row>
     <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="362">
@@ -50985,28 +50985,28 @@
       <c r="I47" s="367"/>
     </row>
     <row r="48" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="424"/>
-      <c r="B48" s="424"/>
-      <c r="C48" s="424"/>
-      <c r="D48" s="424"/>
-      <c r="E48" s="424"/>
-      <c r="F48" s="424"/>
-      <c r="G48" s="424"/>
-      <c r="H48" s="424"/>
-      <c r="I48" s="424"/>
+      <c r="A48" s="423"/>
+      <c r="B48" s="423"/>
+      <c r="C48" s="423"/>
+      <c r="D48" s="423"/>
+      <c r="E48" s="423"/>
+      <c r="F48" s="423"/>
+      <c r="G48" s="423"/>
+      <c r="H48" s="423"/>
+      <c r="I48" s="423"/>
     </row>
     <row r="49" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="428" t="s">
+      <c r="A49" s="424" t="s">
         <v>503</v>
       </c>
-      <c r="B49" s="428"/>
-      <c r="C49" s="428"/>
-      <c r="D49" s="428"/>
-      <c r="E49" s="428"/>
-      <c r="F49" s="428"/>
-      <c r="G49" s="428"/>
-      <c r="H49" s="428"/>
-      <c r="I49" s="428"/>
+      <c r="B49" s="424"/>
+      <c r="C49" s="424"/>
+      <c r="D49" s="424"/>
+      <c r="E49" s="424"/>
+      <c r="F49" s="424"/>
+      <c r="G49" s="424"/>
+      <c r="H49" s="424"/>
+      <c r="I49" s="424"/>
     </row>
     <row r="50" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="332">
@@ -51123,28 +51123,28 @@
       <c r="I55" s="343"/>
     </row>
     <row r="56" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="424"/>
-      <c r="B56" s="424"/>
-      <c r="C56" s="424"/>
-      <c r="D56" s="424"/>
-      <c r="E56" s="424"/>
-      <c r="F56" s="424"/>
-      <c r="G56" s="424"/>
-      <c r="H56" s="424"/>
-      <c r="I56" s="424"/>
+      <c r="A56" s="423"/>
+      <c r="B56" s="423"/>
+      <c r="C56" s="423"/>
+      <c r="D56" s="423"/>
+      <c r="E56" s="423"/>
+      <c r="F56" s="423"/>
+      <c r="G56" s="423"/>
+      <c r="H56" s="423"/>
+      <c r="I56" s="423"/>
     </row>
     <row r="57" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="429" t="s">
+      <c r="A57" s="425" t="s">
         <v>517</v>
       </c>
-      <c r="B57" s="429"/>
-      <c r="C57" s="429"/>
-      <c r="D57" s="429"/>
-      <c r="E57" s="429"/>
-      <c r="F57" s="429"/>
-      <c r="G57" s="429"/>
-      <c r="H57" s="429"/>
-      <c r="I57" s="429"/>
+      <c r="B57" s="425"/>
+      <c r="C57" s="425"/>
+      <c r="D57" s="425"/>
+      <c r="E57" s="425"/>
+      <c r="F57" s="425"/>
+      <c r="G57" s="425"/>
+      <c r="H57" s="425"/>
+      <c r="I57" s="425"/>
     </row>
     <row r="58" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="350">
@@ -51185,28 +51185,28 @@
       <c r="I59" s="343"/>
     </row>
     <row r="60" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="424"/>
-      <c r="B60" s="424"/>
-      <c r="C60" s="424"/>
-      <c r="D60" s="424"/>
-      <c r="E60" s="424"/>
-      <c r="F60" s="424"/>
-      <c r="G60" s="424"/>
-      <c r="H60" s="424"/>
-      <c r="I60" s="424"/>
+      <c r="A60" s="423"/>
+      <c r="B60" s="423"/>
+      <c r="C60" s="423"/>
+      <c r="D60" s="423"/>
+      <c r="E60" s="423"/>
+      <c r="F60" s="423"/>
+      <c r="G60" s="423"/>
+      <c r="H60" s="423"/>
+      <c r="I60" s="423"/>
     </row>
     <row r="61" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="430" t="s">
+      <c r="A61" s="426" t="s">
         <v>523</v>
       </c>
-      <c r="B61" s="430"/>
-      <c r="C61" s="430"/>
-      <c r="D61" s="430"/>
-      <c r="E61" s="430"/>
-      <c r="F61" s="430"/>
-      <c r="G61" s="430"/>
-      <c r="H61" s="430"/>
-      <c r="I61" s="430"/>
+      <c r="B61" s="426"/>
+      <c r="C61" s="426"/>
+      <c r="D61" s="426"/>
+      <c r="E61" s="426"/>
+      <c r="F61" s="426"/>
+      <c r="G61" s="426"/>
+      <c r="H61" s="426"/>
+      <c r="I61" s="426"/>
     </row>
     <row r="62" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="368">
@@ -51266,25 +51266,18 @@
       <c r="I64" s="373"/>
     </row>
     <row r="65" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="424"/>
-      <c r="B65" s="424"/>
-      <c r="C65" s="424"/>
-      <c r="D65" s="424"/>
-      <c r="E65" s="424"/>
-      <c r="F65" s="424"/>
-      <c r="G65" s="424"/>
-      <c r="H65" s="424"/>
-      <c r="I65" s="424"/>
+      <c r="A65" s="423"/>
+      <c r="B65" s="423"/>
+      <c r="C65" s="423"/>
+      <c r="D65" s="423"/>
+      <c r="E65" s="423"/>
+      <c r="F65" s="423"/>
+      <c r="G65" s="423"/>
+      <c r="H65" s="423"/>
+      <c r="I65" s="423"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -51296,6 +51289,13 @@
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="E7:E502" xr:uid="{7D176FDF-4349-44A6-92F9-BC666AEC5B80}">
@@ -51363,33 +51363,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="381" t="s">
+      <c r="O3" s="394" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="381"/>
-      <c r="Q3" s="381"/>
-      <c r="R3" s="381"/>
-      <c r="S3" s="381"/>
-      <c r="T3" s="381"/>
-      <c r="U3" s="381"/>
-      <c r="V3" s="381"/>
-      <c r="W3" s="381"/>
-      <c r="X3" s="381"/>
+      <c r="P3" s="394"/>
+      <c r="Q3" s="394"/>
+      <c r="R3" s="394"/>
+      <c r="S3" s="394"/>
+      <c r="T3" s="394"/>
+      <c r="U3" s="394"/>
+      <c r="V3" s="394"/>
+      <c r="W3" s="394"/>
+      <c r="X3" s="394"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="381"/>
-      <c r="P4" s="381"/>
-      <c r="Q4" s="381"/>
-      <c r="R4" s="381"/>
-      <c r="S4" s="381"/>
-      <c r="T4" s="381"/>
-      <c r="U4" s="381"/>
-      <c r="V4" s="381"/>
-      <c r="W4" s="381"/>
-      <c r="X4" s="381"/>
+      <c r="O4" s="394"/>
+      <c r="P4" s="394"/>
+      <c r="Q4" s="394"/>
+      <c r="R4" s="394"/>
+      <c r="S4" s="394"/>
+      <c r="T4" s="394"/>
+      <c r="U4" s="394"/>
+      <c r="V4" s="394"/>
+      <c r="W4" s="394"/>
+      <c r="X4" s="394"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -51418,16 +51418,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="75"/>
-      <c r="J8" s="408" t="s">
+      <c r="J8" s="403" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="408"/>
-      <c r="L8" s="408"/>
-      <c r="M8" s="408"/>
-      <c r="N8" s="408"/>
-      <c r="O8" s="408"/>
-      <c r="P8" s="408"/>
-      <c r="Q8" s="408"/>
+      <c r="K8" s="403"/>
+      <c r="L8" s="403"/>
+      <c r="M8" s="403"/>
+      <c r="N8" s="403"/>
+      <c r="O8" s="403"/>
+      <c r="P8" s="403"/>
+      <c r="Q8" s="403"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -51438,107 +51438,107 @@
       </c>
       <c r="V8" s="73"/>
       <c r="W8" s="73"/>
-      <c r="X8" s="412" t="s">
+      <c r="X8" s="404" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="413"/>
-      <c r="Z8" s="413"/>
-      <c r="AA8" s="414"/>
-      <c r="AB8" s="415" t="s">
+      <c r="Y8" s="405"/>
+      <c r="Z8" s="405"/>
+      <c r="AA8" s="406"/>
+      <c r="AB8" s="407" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="417" t="s">
+      <c r="AC8" s="409" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="418"/>
-      <c r="AE8" s="418"/>
-      <c r="AF8" s="418"/>
-      <c r="AG8" s="418"/>
-      <c r="AH8" s="418"/>
-      <c r="AI8" s="405" t="s">
+      <c r="AD8" s="410"/>
+      <c r="AE8" s="410"/>
+      <c r="AF8" s="410"/>
+      <c r="AG8" s="410"/>
+      <c r="AH8" s="410"/>
+      <c r="AI8" s="414" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="405"/>
-      <c r="AK8" s="405"/>
-      <c r="AL8" s="405"/>
-      <c r="AM8" s="405"/>
-      <c r="AN8" s="405"/>
-      <c r="AO8" s="402" t="s">
+      <c r="AJ8" s="414"/>
+      <c r="AK8" s="414"/>
+      <c r="AL8" s="414"/>
+      <c r="AM8" s="414"/>
+      <c r="AN8" s="414"/>
+      <c r="AO8" s="420" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="402"/>
-      <c r="AQ8" s="402"/>
-      <c r="AR8" s="402"/>
-      <c r="AS8" s="392" t="s">
+      <c r="AP8" s="420"/>
+      <c r="AQ8" s="420"/>
+      <c r="AR8" s="420"/>
+      <c r="AS8" s="390" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="392"/>
-      <c r="AU8" s="392"/>
+      <c r="AT8" s="390"/>
+      <c r="AU8" s="390"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="407" t="s">
+      <c r="C9" s="416" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="407"/>
-      <c r="E9" s="407"/>
-      <c r="F9" s="407"/>
-      <c r="G9" s="407"/>
-      <c r="H9" s="407"/>
-      <c r="I9" s="407"/>
-      <c r="J9" s="408" t="s">
+      <c r="D9" s="416"/>
+      <c r="E9" s="416"/>
+      <c r="F9" s="416"/>
+      <c r="G9" s="416"/>
+      <c r="H9" s="416"/>
+      <c r="I9" s="416"/>
+      <c r="J9" s="403" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="408"/>
-      <c r="L9" s="408"/>
-      <c r="M9" s="408"/>
-      <c r="N9" s="408"/>
-      <c r="O9" s="408"/>
-      <c r="P9" s="408"/>
-      <c r="Q9" s="408"/>
+      <c r="K9" s="403"/>
+      <c r="L9" s="403"/>
+      <c r="M9" s="403"/>
+      <c r="N9" s="403"/>
+      <c r="O9" s="403"/>
+      <c r="P9" s="403"/>
+      <c r="Q9" s="403"/>
       <c r="R9" s="79"/>
       <c r="S9" s="80"/>
       <c r="T9" s="80"/>
       <c r="U9" s="80"/>
-      <c r="V9" s="412" t="s">
+      <c r="V9" s="404" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="413"/>
-      <c r="X9" s="413"/>
-      <c r="Y9" s="413"/>
-      <c r="Z9" s="413"/>
-      <c r="AA9" s="414"/>
-      <c r="AB9" s="416"/>
-      <c r="AC9" s="419" t="s">
+      <c r="W9" s="405"/>
+      <c r="X9" s="405"/>
+      <c r="Y9" s="405"/>
+      <c r="Z9" s="405"/>
+      <c r="AA9" s="406"/>
+      <c r="AB9" s="408"/>
+      <c r="AC9" s="413" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="419"/>
-      <c r="AE9" s="419"/>
-      <c r="AF9" s="419"/>
-      <c r="AG9" s="419"/>
-      <c r="AH9" s="419"/>
-      <c r="AI9" s="406" t="s">
+      <c r="AD9" s="413"/>
+      <c r="AE9" s="413"/>
+      <c r="AF9" s="413"/>
+      <c r="AG9" s="413"/>
+      <c r="AH9" s="413"/>
+      <c r="AI9" s="415" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="406"/>
-      <c r="AK9" s="406"/>
-      <c r="AL9" s="406"/>
-      <c r="AM9" s="406"/>
-      <c r="AN9" s="406"/>
-      <c r="AO9" s="403" t="s">
+      <c r="AJ9" s="415"/>
+      <c r="AK9" s="415"/>
+      <c r="AL9" s="415"/>
+      <c r="AM9" s="415"/>
+      <c r="AN9" s="415"/>
+      <c r="AO9" s="421" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="403"/>
-      <c r="AQ9" s="403"/>
-      <c r="AR9" s="403"/>
-      <c r="AS9" s="404" t="s">
+      <c r="AP9" s="421"/>
+      <c r="AQ9" s="421"/>
+      <c r="AR9" s="421"/>
+      <c r="AS9" s="422" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="404"/>
-      <c r="AU9" s="404"/>
+      <c r="AT9" s="422"/>
+      <c r="AU9" s="422"/>
       <c r="AV9" s="81" t="s">
         <v>212</v>
       </c>
@@ -57685,11 +57685,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -57700,6 +57695,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -57753,41 +57753,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="432" t="s">
+      <c r="A2" s="435" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="432"/>
-      <c r="C2" s="432"/>
+      <c r="B2" s="435"/>
+      <c r="C2" s="435"/>
       <c r="D2" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="432" t="s">
+      <c r="E2" s="435" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="432"/>
+      <c r="F2" s="435"/>
       <c r="G2" s="175" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="431" t="s">
+      <c r="H2" s="434" t="s">
         <v>337</v>
       </c>
-      <c r="I2" s="431"/>
-      <c r="J2" s="431"/>
-      <c r="K2" s="431" t="s">
+      <c r="I2" s="434"/>
+      <c r="J2" s="434"/>
+      <c r="K2" s="434" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="432"/>
-      <c r="M2" s="432"/>
-      <c r="N2" s="431" t="s">
+      <c r="L2" s="435"/>
+      <c r="M2" s="435"/>
+      <c r="N2" s="434" t="s">
         <v>338</v>
       </c>
-      <c r="O2" s="432"/>
-      <c r="P2" s="432"/>
-      <c r="Q2" s="433"/>
-      <c r="R2" s="431" t="s">
+      <c r="O2" s="435"/>
+      <c r="P2" s="435"/>
+      <c r="Q2" s="436"/>
+      <c r="R2" s="434" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="432"/>
+      <c r="S2" s="435"/>
     </row>
     <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="83" t="s">
@@ -58299,12 +58299,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -58442,6 +58436,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -58452,22 +58452,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58485,6 +58469,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
